--- a/xlsx/packagedataCN20260413 special cargo-FR.xlsx
+++ b/xlsx/packagedataCN20260413 special cargo-FR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5E026C-E65F-4D15-91DA-917FF114FE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28B26E3-114E-4889-9707-A5679F739374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,65 +25,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宽度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否堆叠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包装名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包装方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>托盘</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>托盘可叉方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否包箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否转向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>单向可叉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>pkg05-54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Width</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Height</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Packing Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forklift Direction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need Boxing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boxing Quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotatable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stackable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -424,54 +428,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="B2">
         <v>350</v>
@@ -489,24 +497,27 @@
         <v>11000</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -524,24 +535,27 @@
         <v>11000</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>330</v>
@@ -559,24 +573,27 @@
         <v>10500</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>330</v>
@@ -594,18 +611,21 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
         <v>0</v>
       </c>
     </row>
